--- a/output/30day_sales_AlNoor_cleaned.xlsx
+++ b/output/30day_sales_AlNoor_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\Fyp\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8FAFC17-9EF4-4CB5-92B1-2DF4DD25F7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BD3EBB-A4BC-4363-BC89-41451F25BABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
